--- a/01_processed_data/classification/境内策略ETF产品池_代表产品筛选版.xlsx
+++ b/01_processed_data/classification/境内策略ETF产品池_代表产品筛选版.xlsx
@@ -14,7 +14,7 @@
     <sheet name="代表产品统计" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品池_代表产品筛选版'!$A$1:$AI$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品池_代表产品筛选版'!$A$1:$AM$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Step7代表产品清单'!$A$1:$AI$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'主线代表产品'!$A$1:$AI$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'补充观察代表产品'!$A$1:$AI$8</definedName>
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,6 +85,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI59"/>
+  <dimension ref="A1:AM59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -489,6 +492,10 @@
     <col width="48" customWidth="1" min="33" max="33"/>
     <col width="48" customWidth="1" min="34" max="34"/>
     <col width="33" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
+    <col width="48" customWidth="1" min="37" max="37"/>
+    <col width="48" customWidth="1" min="38" max="38"/>
+    <col width="48" customWidth="1" min="39" max="39"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -667,6 +674,26 @@
           <t>Step7备注</t>
         </is>
       </c>
+      <c r="AJ1" s="4" t="inlineStr">
+        <is>
+          <t>Step8指数规则核验状态</t>
+        </is>
+      </c>
+      <c r="AK1" s="4" t="inlineStr">
+        <is>
+          <t>Step8指数规则简述</t>
+        </is>
+      </c>
+      <c r="AL1" s="4" t="inlineStr">
+        <is>
+          <t>Step8信息来源URL</t>
+        </is>
+      </c>
+      <c r="AM1" s="4" t="inlineStr">
+        <is>
+          <t>Step8待补充事项</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -828,6 +855,26 @@
           <t>作为红利类第一优先级代表</t>
         </is>
       </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>传统沪市红利策略，强调高股息、分红稳定和可投资性，是境内红利ETF最经典的指数之一；选样方法：在样本空间内按过去三年平均现金股息率由高到低排名，选取前50只证券；加权方式：股息率加权；调样频率：每年12月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/000015_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -983,6 +1030,26 @@
       <c r="AI3" s="2" t="inlineStr">
         <is>
           <t>后续需补规模和成交额</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>A股全市场红利代表指数，较上证红利覆盖范围更广，是中证体系红利策略的核心；选样方法：在样本空间内按过去三年平均现金股息率由高到低排名，选取前100只上市公司证券；加权方式：股息率加权；调样频率：每年12月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208175433-000922_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM3" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
         </is>
       </c>
     </row>
@@ -1126,6 +1193,26 @@
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr"/>
       <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>A股全市场红利代表指数，较上证红利覆盖范围更广，是中证体系红利策略的核心；选样方法：在样本空间内按过去三年平均现金股息率由高到低排名，选取前100只上市公司证券；加权方式：股息率加权；调样频率：每年12月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208175433-000922_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM4" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1271,6 +1358,26 @@
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr"/>
       <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="inlineStr">
+        <is>
+          <t>A股全市场红利代表指数，较上证红利覆盖范围更广，是中证体系红利策略的核心；选样方法：在样本空间内按过去三年平均现金股息率由高到低排名，选取前100只上市公司证券；加权方式：股息率加权；调样频率：每年12月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208175433-000922_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM5" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1416,6 +1523,26 @@
       <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr"/>
       <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>A股全市场红利代表指数，较上证红利覆盖范围更广，是中证体系红利策略的核心；选样方法：在样本空间内按过去三年平均现金股息率由高到低排名，选取前100只上市公司证券；加权方式：股息率加权；调样频率：每年12月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208175433-000922_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM6" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1561,6 +1688,26 @@
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr"/>
       <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK7" s="2" t="inlineStr">
+        <is>
+          <t>A股全市场红利代表指数，较上证红利覆盖范围更广，是中证体系红利策略的核心；选样方法：在样本空间内按过去三年平均现金股息率由高到低排名，选取前100只上市公司证券；加权方式：股息率加权；调样频率：每年12月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208175433-000922_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM7" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1706,6 +1853,26 @@
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr"/>
       <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>A股全市场红利代表指数，较上证红利覆盖范围更广，是中证体系红利策略的核心；选样方法：在样本空间内按过去三年平均现金股息率由高到低排名，选取前100只上市公司证券；加权方式：股息率加权；调样频率：每年12月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208175433-000922_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM8" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1861,6 +2028,26 @@
       <c r="AI9" s="2" t="inlineStr">
         <is>
           <t>适合作为深市红利代表</t>
+        </is>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>部分核验</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="inlineStr">
+        <is>
+          <t>深市红利代表指数，与上证红利和中证红利形成市场板块对比；选样方法：国证官网公开页面显示：剔除预期净资产收益率处于后50%且净资产收益率变化率处于后20%的股票，选取累计分红金额和日均成交金额综合排名位于前40名的股票作为样本股；加权方式：待二次核验；公开页面未完整展示权重细则；调样频率：待二次核验</t>
+        </is>
+      </c>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/module/index-detail.html?act_menu=1&amp;indexCode=399324</t>
+        </is>
+      </c>
+      <c r="AM9" s="2" t="inlineStr">
+        <is>
+          <t>部分核验：需后续下载完整编制方案或用Wind校验权重和调样规则；前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
         </is>
       </c>
     </row>
@@ -2008,6 +2195,26 @@
       <c r="AG10" s="2" t="inlineStr"/>
       <c r="AH10" s="2" t="inlineStr"/>
       <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>部分核验</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="inlineStr">
+        <is>
+          <t>深市红利代表指数，与上证红利和中证红利形成市场板块对比；选样方法：国证官网公开页面显示：剔除预期净资产收益率处于后50%且净资产收益率变化率处于后20%的股票，选取累计分红金额和日均成交金额综合排名位于前40名的股票作为样本股；加权方式：待二次核验；公开页面未完整展示权重细则；调样频率：待二次核验</t>
+        </is>
+      </c>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/module/index-detail.html?act_menu=1&amp;indexCode=399324</t>
+        </is>
+      </c>
+      <c r="AM10" s="2" t="inlineStr">
+        <is>
+          <t>部分核验：需后续下载完整编制方案或用Wind校验权重和调样规则；前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2153,6 +2360,18 @@
       <c r="AG11" s="2" t="inlineStr"/>
       <c r="AH11" s="2" t="inlineStr"/>
       <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2314,6 +2533,26 @@
           <t>作为红利低波第一优先级代表</t>
         </is>
       </c>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="inlineStr">
+        <is>
+          <t>红利+低波复合策略，通过高股息和低波动筛选增强防御属性；选样方法：先剔除红利支付率过高或为负、每股股息增长率非正的证券；再按三年平均税后现金股息率选前75只；最后按过去一年波动率升序选前50只；加权方式：股息率加权；调样频率：每年12月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/H30269_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM12" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2473,6 +2712,26 @@
       <c r="AI13" s="2" t="inlineStr">
         <is>
           <t>用于比较红利低波50/100口径差异</t>
+        </is>
+      </c>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="inlineStr">
+        <is>
+          <t>比中证红利低波动指数成分更多、更分散，使用股息率/波动率加权；选样方法：剔除过去一年日均成交金额排名后20%；选取过去三年连续现金分红且每年现金股息率大于0的证券；先按股息率选前300只，再按过去一年波动率升序选前100只；加权方式：股息率/过去一年波动率加权；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208180204-930955_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM13" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
         </is>
       </c>
     </row>
@@ -2632,6 +2891,18 @@
       <c r="AG14" s="2" t="inlineStr"/>
       <c r="AH14" s="2" t="inlineStr"/>
       <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2777,6 +3048,18 @@
       <c r="AG15" s="2" t="inlineStr"/>
       <c r="AH15" s="2" t="inlineStr"/>
       <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2922,6 +3205,26 @@
       <c r="AG16" s="2" t="inlineStr"/>
       <c r="AH16" s="2" t="inlineStr"/>
       <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="inlineStr">
+        <is>
+          <t>A500样本空间上的红利低波策略，体现新宽基生态与红利低波因子的结合；选样方法：在中证A500样本中选取过去三年连续现金分红、股利支付率合理、过去12个季度ROE标准差排名前80%的证券；按过去三年平均现金股息率选前50%作为待选样本；再按过去一年波动率升序选前50只；加权方式：股息率加权；调样频率：每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/932422_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM16" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3081,6 +3384,26 @@
       <c r="AI17" s="2" t="inlineStr">
         <is>
           <t>新产品，后续需校验规模和流动性</t>
+        </is>
+      </c>
+      <c r="AJ17" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="inlineStr">
+        <is>
+          <t>A500样本空间上的红利低波策略，体现新宽基生态与红利低波因子的结合；选样方法：在中证A500样本中选取过去三年连续现金分红、股利支付率合理、过去12个季度ROE标准差排名前80%的证券；按过去三年平均现金股息率选前50%作为待选样本；再按过去一年波动率升序选前50只；加权方式：股息率加权；调样频率：每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/932422_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM17" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
         </is>
       </c>
     </row>
@@ -3228,6 +3551,26 @@
       <c r="AG18" s="2" t="inlineStr"/>
       <c r="AH18" s="2" t="inlineStr"/>
       <c r="AI18" s="2" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="inlineStr">
+        <is>
+          <t>A500样本空间上的红利低波策略，体现新宽基生态与红利低波因子的结合；选样方法：在中证A500样本中选取过去三年连续现金分红、股利支付率合理、过去12个季度ROE标准差排名前80%的证券；按过去三年平均现金股息率选前50%作为待选样本；再按过去一年波动率升序选前50只；加权方式：股息率加权；调样频率：每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/932422_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM18" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3373,6 +3716,26 @@
       <c r="AG19" s="2" t="inlineStr"/>
       <c r="AH19" s="2" t="inlineStr"/>
       <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="inlineStr">
+        <is>
+          <t>比中证红利低波动指数成分更多、更分散，使用股息率/波动率加权；选样方法：剔除过去一年日均成交金额排名后20%；选取过去三年连续现金分红且每年现金股息率大于0的证券；先按股息率选前300只，再按过去一年波动率升序选前100只；加权方式：股息率/过去一年波动率加权；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208180204-930955_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM19" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3542,6 +3905,26 @@
           <t>作为低波类第一代表</t>
         </is>
       </c>
+      <c r="AJ20" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="inlineStr">
+        <is>
+          <t>大盘低波策略，核心是降低波动同时减少行业偏离；选样方法：在沪深300一级行业内计算过去一年日收益率波动率并由低到高排名；按沪深300一级行业样本分布确定行业配额，选取低波证券并调整至100只；加权方式：行业权重保持与沪深300一级行业权重相同；行业内按波动率倒数加权；调样频率：每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/527_930846_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM20" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -3699,6 +4082,26 @@
           <t>规模可能较小，但策略代表性较强</t>
         </is>
       </c>
+      <c r="AJ21" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="inlineStr">
+        <is>
+          <t>中盘低波策略，与沪深300低波形成市值层面对比；选样方法：在中证500二级行业内计算过去一年日收益率波动率并排序；按中证500二级行业样本分布确定配额，选取低波证券并调整至150只；加权方式：行业内按波动率倒数加权；调样频率：每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/480_930782_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM21" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3864,6 +4267,26 @@
           <t>作为自由现金流第一优先级代表</t>
         </is>
       </c>
+      <c r="AJ22" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="inlineStr">
+        <is>
+          <t>强调企业真实现金创造能力和现金流稳定性，是自由现金流策略核心指数；选样方法：剔除最近半年日均成交金额后20%、金融或房地产行业、近12季度ROE稳定性后10%；选取自由现金流、企业价值和近三年经营现金流为正且现金流质量较好的证券；按近一年自由现金流率选前100只；加权方式：按样本公司自由现金流计算初始权重；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一个交易日实施</t>
+        </is>
+      </c>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_980092.pdf</t>
+        </is>
+      </c>
+      <c r="AM22" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4027,6 +4450,26 @@
       <c r="AI23" s="2" t="inlineStr">
         <is>
           <t>后续需和159201做横向比较</t>
+        </is>
+      </c>
+      <c r="AJ23" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="inlineStr">
+        <is>
+          <t>强调企业真实现金创造能力和现金流稳定性，是自由现金流策略核心指数；选样方法：剔除最近半年日均成交金额后20%、金融或房地产行业、近12季度ROE稳定性后10%；选取自由现金流、企业价值和近三年经营现金流为正且现金流质量较好的证券；按近一年自由现金流率选前100只；加权方式：按样本公司自由现金流计算初始权重；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一个交易日实施</t>
+        </is>
+      </c>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_980092.pdf</t>
+        </is>
+      </c>
+      <c r="AM23" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
         </is>
       </c>
     </row>
@@ -4174,6 +4617,18 @@
       <c r="AG24" s="2" t="inlineStr"/>
       <c r="AH24" s="2" t="inlineStr"/>
       <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -4323,6 +4778,18 @@
       <c r="AG25" s="2" t="inlineStr"/>
       <c r="AH25" s="2" t="inlineStr"/>
       <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr"/>
+      <c r="AM25" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -4472,6 +4939,18 @@
       <c r="AG26" s="2" t="inlineStr"/>
       <c r="AH26" s="2" t="inlineStr"/>
       <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr"/>
+      <c r="AM26" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -4635,6 +5114,26 @@
       <c r="AI27" s="2" t="inlineStr">
         <is>
           <t>后续需校验规模和成交额</t>
+        </is>
+      </c>
+      <c r="AJ27" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="inlineStr">
+        <is>
+          <t>中证体系自由现金流指数，便于和国证自由现金流进行规则差异对比；选样方法：过去一年日均成交金额排名位于前80%；剔除金融和地产；要求自由现金流和企业价值为正、连续5年经营现金流为正、盈利质量前80%；按自由现金流率选前100只；加权方式：自由现金流加权；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/932365_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM27" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
         </is>
       </c>
     </row>
@@ -4786,6 +5285,26 @@
       <c r="AG28" s="2" t="inlineStr"/>
       <c r="AH28" s="2" t="inlineStr"/>
       <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>中证体系自由现金流指数，便于和国证自由现金流进行规则差异对比；选样方法：过去一年日均成交金额排名位于前80%；剔除金融和地产；要求自由现金流和企业价值为正、连续5年经营现金流为正、盈利质量前80%；按自由现金流率选前100只；加权方式：自由现金流加权；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/932365_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM28" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4935,6 +5454,26 @@
       <c r="AG29" s="2" t="inlineStr"/>
       <c r="AH29" s="2" t="inlineStr"/>
       <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>强调企业真实现金创造能力和现金流稳定性，是自由现金流策略核心指数；选样方法：剔除最近半年日均成交金额后20%、金融或房地产行业、近12季度ROE稳定性后10%；选取自由现金流、企业价值和近三年经营现金流为正且现金流质量较好的证券；按近一年自由现金流率选前100只；加权方式：按样本公司自由现金流计算初始权重；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一个交易日实施</t>
+        </is>
+      </c>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_980092.pdf</t>
+        </is>
+      </c>
+      <c r="AM29" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5084,6 +5623,26 @@
       <c r="AG30" s="2" t="inlineStr"/>
       <c r="AH30" s="2" t="inlineStr"/>
       <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>强调企业真实现金创造能力和现金流稳定性，是自由现金流策略核心指数；选样方法：剔除最近半年日均成交金额后20%、金融或房地产行业、近12季度ROE稳定性后10%；选取自由现金流、企业价值和近三年经营现金流为正且现金流质量较好的证券；按近一年自由现金流率选前100只；加权方式：按样本公司自由现金流计算初始权重；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一个交易日实施</t>
+        </is>
+      </c>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_980092.pdf</t>
+        </is>
+      </c>
+      <c r="AM30" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5233,6 +5792,26 @@
       <c r="AG31" s="2" t="inlineStr"/>
       <c r="AH31" s="2" t="inlineStr"/>
       <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>强调企业真实现金创造能力和现金流稳定性，是自由现金流策略核心指数；选样方法：剔除最近半年日均成交金额后20%、金融或房地产行业、近12季度ROE稳定性后10%；选取自由现金流、企业价值和近三年经营现金流为正且现金流质量较好的证券；按近一年自由现金流率选前100只；加权方式：按样本公司自由现金流计算初始权重；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一个交易日实施</t>
+        </is>
+      </c>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_980092.pdf</t>
+        </is>
+      </c>
+      <c r="AM31" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -5402,6 +5981,26 @@
           <t>建议重点查指数编制方案</t>
         </is>
       </c>
+      <c r="AJ32" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="inlineStr">
+        <is>
+          <t>红利+质量复合策略，强调分红能力和盈利质量；选样方法：先做市值和成交额可投资性筛选；选取满足分红、再融资和股利支付率条件的证券；计算六个财务质量指标综合得分，选前50只；加权方式：标准化后的综合得分加权；调样频率：每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208180546-931468_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM32" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -5573,6 +6172,26 @@
       <c r="AI33" s="2" t="inlineStr">
         <is>
           <t>新产品，后续需校验规模和流动性</t>
+        </is>
+      </c>
+      <c r="AJ33" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK33" s="2" t="inlineStr">
+        <is>
+          <t>红利质量扩展指数，约束更强调分红稳定、质量和行业分散；选样方法：先做市值和成交额筛选；选取过去三年连续分红且股利支付率合理证券；按股息率剔除后50%；按ROE标准差筛选；再按质量因子综合得分选前50只；加权方式：综合得分倾斜加权；调样频率：每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/932315_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM33" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
         </is>
       </c>
     </row>
@@ -5732,6 +6351,26 @@
       <c r="AG34" s="2" t="inlineStr"/>
       <c r="AH34" s="2" t="inlineStr"/>
       <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK34" s="2" t="inlineStr">
+        <is>
+          <t>红利质量扩展指数，约束更强调分红稳定、质量和行业分散；选样方法：先做市值和成交额筛选；选取过去三年连续分红且股利支付率合理证券；按股息率剔除后50%；按ROE标准差筛选；再按质量因子综合得分选前50只；加权方式：综合得分倾斜加权；调样频率：每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/932315_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM34" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -5897,6 +6536,18 @@
           <t>优先查清楚跟踪指数全称</t>
         </is>
       </c>
+      <c r="AJ35" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK35" s="2" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr"/>
+      <c r="AM35" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6058,6 +6709,26 @@
           <t>新产品，后续需校验规模和成交额</t>
         </is>
       </c>
+      <c r="AJ36" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK36" s="2" t="inlineStr">
+        <is>
+          <t>国证价值指数体系代表，实际是价值+质量约束的复合价值策略；选样方法：剔除近半年成交金额后20%、近半年总市值后20%、净利润小于0证券；剔除ROE均值后20%、ROE波动率前20%、自由现金流率后50%；对市盈率倒数、股息率、自由现金流率标准化后计算价值得分，选前100只；加权方式：以价值得分倾斜因子乘自由流通市值计算初始权重；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一个交易日实施</t>
+        </is>
+      </c>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_980081.pdf</t>
+        </is>
+      </c>
+      <c r="AM36" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6219,6 +6890,26 @@
           <t>后续需确认指数全称</t>
         </is>
       </c>
+      <c r="AJ37" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK37" s="2" t="inlineStr">
+        <is>
+          <t>成长+动量复合策略，适合观察成长因子与趋势动量结合；选样方法：先按过去半年日均自由流通市值选前30%；计算成长和动量六个指标得分；根据因子得分和自由流通市值进行倾斜，选前50只；加权方式：自由流通市值权重基础上的因子倾斜加权；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_399296.pdf</t>
+        </is>
+      </c>
+      <c r="AM37" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -6376,6 +7067,26 @@
           <t>作为深市成长代表</t>
         </is>
       </c>
+      <c r="AJ38" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK38" s="2" t="inlineStr">
+        <is>
+          <t>深市成长风格代表指数，兼顾成长得分和行业内动量表现；选样方法：剔除最近半年日均成交金额或日均总市值后30%、扣非净利润TTM小于0股票；优先纳入成长因子排名靠前的上期样本；剩余股票中选成长因子排名靠前且行业内自由流通市值靠前、动量得分较高证券，共40只；加权方式：派氏加权；具体权重调整因子见国证维护细则；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一个交易日实施</t>
+        </is>
+      </c>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_399326.pdf</t>
+        </is>
+      </c>
+      <c r="AM38" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -6531,6 +7242,26 @@
       <c r="AI39" s="2" t="inlineStr">
         <is>
           <t>适合作为科创成长代表</t>
+        </is>
+      </c>
+      <c r="AJ39" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK39" s="2" t="inlineStr">
+        <is>
+          <t>科创板内部成长风格代表，体现成长因子与科创板样本空间结合；选样方法：过去一年日均成交金额排名前90%；计算最新季度营收TTM环比增长率、扣非净利润TTM环比增长率、过去12季度相关增长率和增长趋势，综合得分选前50只；加权方式：自由流通市值调整后的市值加权并设权重因子；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/000690_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM39" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
         </is>
       </c>
     </row>
@@ -6674,6 +7405,26 @@
       <c r="AG40" s="2" t="inlineStr"/>
       <c r="AH40" s="2" t="inlineStr"/>
       <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK40" s="2" t="inlineStr">
+        <is>
+          <t>科创板内部成长风格代表，体现成长因子与科创板样本空间结合；选样方法：过去一年日均成交金额排名前90%；计算最新季度营收TTM环比增长率、扣非净利润TTM环比增长率、过去12季度相关增长率和增长趋势，综合得分选前50只；加权方式：自由流通市值调整后的市值加权并设权重因子；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/000690_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM40" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -6819,6 +7570,26 @@
       <c r="AG41" s="2" t="inlineStr"/>
       <c r="AH41" s="2" t="inlineStr"/>
       <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK41" s="2" t="inlineStr">
+        <is>
+          <t>科创板内部成长风格代表，体现成长因子与科创板样本空间结合；选样方法：过去一年日均成交金额排名前90%；计算最新季度营收TTM环比增长率、扣非净利润TTM环比增长率、过去12季度相关增长率和增长趋势，综合得分选前50只；加权方式：自由流通市值调整后的市值加权并设权重因子；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/000690_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM41" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -6960,6 +7731,26 @@
       <c r="AG42" s="2" t="inlineStr"/>
       <c r="AH42" s="2" t="inlineStr"/>
       <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK42" s="2" t="inlineStr">
+        <is>
+          <t>科创板内部成长风格代表，体现成长因子与科创板样本空间结合；选样方法：过去一年日均成交金额排名前90%；计算最新季度营收TTM环比增长率、扣非净利润TTM环比增长率、过去12季度相关增长率和增长趋势，综合得分选前50只；加权方式：自由流通市值调整后的市值加权并设权重因子；调样频率：每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/000690_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM42" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -7121,6 +7912,26 @@
           <t>作为基本面策略第一代表</t>
         </is>
       </c>
+      <c r="AJ43" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK43" s="2" t="inlineStr">
+        <is>
+          <t>非市值加权代表策略，用基本面经济规模替代市值权重；选样方法：剔除过去一年日均成交金额排名后20%；计算过去5年营业收入、现金流、净资产、分红四项基本面指标的相对占比，得到基本面价值，选基本面价值最大前50只；加权方式：经自由流通比例调整后的基本面价值加权；调样频率：每年6月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208175416-000925_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM43" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -7278,6 +8089,26 @@
           <t>后续查指数规则</t>
         </is>
       </c>
+      <c r="AJ44" s="2" t="inlineStr">
+        <is>
+          <t>已核验</t>
+        </is>
+      </c>
+      <c r="AK44" s="2" t="inlineStr">
+        <is>
+          <t>深市基本面加权策略代表，适合与基本面50对比样本空间和成分数量；选样方法：剔除过去一年日均成交金额排名后20%；计算基本面价值，选取基本面价值排名前120名证券；加权方式：经自由流通比例调整后的基本面价值加权；调样频率：每年6月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/289_399701_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM44" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -7451,6 +8282,26 @@
           <t>需要和mentor确认是否纳入主线</t>
         </is>
       </c>
+      <c r="AJ45" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验</t>
+        </is>
+      </c>
+      <c r="AK45" s="2" t="inlineStr">
+        <is>
+          <t>指数增强ETF应单列观察，不与纯策略指数ETF混入同一规则表比较；选样方法：该产品属于指数增强ETF，不是跟踪预先编制的Smart Beta策略指数；应查基金招募说明书中的增强策略和跟踪误差约束；加权方式：不适用；调样频率：不适用</t>
+        </is>
+      </c>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>待补充基金招募说明书URL</t>
+        </is>
+      </c>
+      <c r="AM45" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验：后续若mentor要求纳入，再查招募说明书</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -7624,6 +8475,26 @@
           <t>需要和mentor确认是否纳入主线</t>
         </is>
       </c>
+      <c r="AJ46" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验</t>
+        </is>
+      </c>
+      <c r="AK46" s="2" t="inlineStr">
+        <is>
+          <t>A500生态下指数增强代表，需单独作为增强ETF观察样本；选样方法：该产品属于指数增强ETF，不是跟踪预先编制的Smart Beta策略指数；应查基金招募说明书中的增强策略和跟踪误差约束；加权方式：不适用；调样频率：不适用</t>
+        </is>
+      </c>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>待补充基金招募说明书URL</t>
+        </is>
+      </c>
+      <c r="AM46" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验：后续若mentor要求纳入，再查招募说明书</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -7795,6 +8666,26 @@
       <c r="AI47" s="2" t="inlineStr">
         <is>
           <t>不进入A股主线，先放补充</t>
+        </is>
+      </c>
+      <c r="AJ47" s="2" t="inlineStr">
+        <is>
+          <t>部分核验</t>
+        </is>
+      </c>
+      <c r="AK47" s="2" t="inlineStr">
+        <is>
+          <t>中国特色股东回报策略，兼具央企主题和分红/回购回报属性；选样方法：主要选取国务院国资委下属现金分红或回购总额占总市值比率较高的50只上市公司证券；加权方式：待进一步查完整加权规则；指数目标为股东回报主题；调样频率：每年调整</t>
+        </is>
+      </c>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208180042-932039_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM47" s="2" t="inlineStr">
+        <is>
+          <t>部分核验：补充观察，不进入A股纯策略主线；前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
         </is>
       </c>
     </row>
@@ -7954,6 +8845,26 @@
       <c r="AG48" s="2" t="inlineStr"/>
       <c r="AH48" s="2" t="inlineStr"/>
       <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr">
+        <is>
+          <t>部分核验</t>
+        </is>
+      </c>
+      <c r="AK48" s="2" t="inlineStr">
+        <is>
+          <t>中国特色股东回报策略，兼具央企主题和分红/回购回报属性；选样方法：主要选取国务院国资委下属现金分红或回购总额占总市值比率较高的50只上市公司证券；加权方式：待进一步查完整加权规则；指数目标为股东回报主题；调样频率：每年调整</t>
+        </is>
+      </c>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208180042-932039_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM48" s="2" t="inlineStr">
+        <is>
+          <t>部分核验：补充观察，不进入A股纯策略主线；前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -8111,6 +9022,26 @@
       <c r="AG49" s="2" t="inlineStr"/>
       <c r="AH49" s="2" t="inlineStr"/>
       <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr">
+        <is>
+          <t>部分核验</t>
+        </is>
+      </c>
+      <c r="AK49" s="2" t="inlineStr">
+        <is>
+          <t>中国特色股东回报策略，兼具央企主题和分红/回购回报属性；选样方法：主要选取国务院国资委下属现金分红或回购总额占总市值比率较高的50只上市公司证券；加权方式：待进一步查完整加权规则；指数目标为股东回报主题；调样频率：每年调整</t>
+        </is>
+      </c>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208180042-932039_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM49" s="2" t="inlineStr">
+        <is>
+          <t>部分核验：补充观察，不进入A股纯策略主线；前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -8282,6 +9213,26 @@
       <c r="AI50" s="2" t="inlineStr">
         <is>
           <t>后续问mentor是否纳入红利主线</t>
+        </is>
+      </c>
+      <c r="AJ50" s="2" t="inlineStr">
+        <is>
+          <t>部分核验</t>
+        </is>
+      </c>
+      <c r="AK50" s="2" t="inlineStr">
+        <is>
+          <t>央企范围内的红利策略，是红利策略的中国特色延伸；选样方法：从中央企业中选取现金股息率高、分红比较稳定且有一定规模及流动性的50只证券；加权方式：待进一步查完整加权规则；大概率为股息率相关加权，需二次核验；调样频率：待进一步核验</t>
+        </is>
+      </c>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208175355-000825_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM50" s="2" t="inlineStr">
+        <is>
+          <t>部分核验：补充观察，是否纳入红利主线需问mentor；前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
         </is>
       </c>
     </row>
@@ -8441,6 +9392,18 @@
       <c r="AG51" s="2" t="inlineStr"/>
       <c r="AH51" s="2" t="inlineStr"/>
       <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK51" s="2" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr"/>
+      <c r="AM51" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -8598,6 +9561,18 @@
       <c r="AG52" s="2" t="inlineStr"/>
       <c r="AH52" s="2" t="inlineStr"/>
       <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK52" s="2" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr"/>
+      <c r="AM52" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -8755,6 +9730,18 @@
       <c r="AG53" s="2" t="inlineStr"/>
       <c r="AH53" s="2" t="inlineStr"/>
       <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK53" s="2" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr"/>
+      <c r="AM53" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -8900,6 +9887,26 @@
       <c r="AG54" s="2" t="inlineStr"/>
       <c r="AH54" s="2" t="inlineStr"/>
       <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr">
+        <is>
+          <t>部分核验</t>
+        </is>
+      </c>
+      <c r="AK54" s="2" t="inlineStr">
+        <is>
+          <t>央企主题和ESG评分结合，暂作为ESG补充观察；选样方法：公开新闻显示该指数依据中证ESG评价中环境、社会、公司治理评价得分，选取ESG综合得分最高的50只央企上市公司证券；完整编制方案需后续在中证官网二次核验；加权方式：待二次核验；调样频率：待二次核验</t>
+        </is>
+      </c>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sse.com.cn/disclosure/fund/announcement/c/new/2024-12-10/560810_20241210_D138.pdf</t>
+        </is>
+      </c>
+      <c r="AM54" s="2" t="inlineStr">
+        <is>
+          <t>部分核验：只核验到基金文件和公开新闻，未找到完整官方PDF，后续需补；前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -9061,6 +10068,26 @@
           <t>不进入主线，先放补充</t>
         </is>
       </c>
+      <c r="AJ55" s="2" t="inlineStr">
+        <is>
+          <t>部分核验</t>
+        </is>
+      </c>
+      <c r="AK55" s="2" t="inlineStr">
+        <is>
+          <t>央企主题和ESG评分结合，暂作为ESG补充观察；选样方法：公开新闻显示该指数依据中证ESG评价中环境、社会、公司治理评价得分，选取ESG综合得分最高的50只央企上市公司证券；完整编制方案需后续在中证官网二次核验；加权方式：待二次核验；调样频率：待二次核验</t>
+        </is>
+      </c>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sse.com.cn/disclosure/fund/announcement/c/new/2024-12-10/560810_20241210_D138.pdf</t>
+        </is>
+      </c>
+      <c r="AM55" s="2" t="inlineStr">
+        <is>
+          <t>部分核验：只核验到基金文件和公开新闻，未找到完整官方PDF，后续需补；前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -9220,6 +10247,26 @@
       <c r="AI56" s="2" t="inlineStr">
         <is>
           <t>不进入主线，先放补充</t>
+        </is>
+      </c>
+      <c r="AJ56" s="2" t="inlineStr">
+        <is>
+          <t>部分核验</t>
+        </is>
+      </c>
+      <c r="AK56" s="2" t="inlineStr">
+        <is>
+          <t>可持续发展/ESG策略补充样本，不作为今天A股因子主线；选样方法：先从产业政策、特殊行业、财务问题、负面事件、违法违规及特殊处理等方面剔除不符合资质证券，再基于可持续发展评估模型选取评分最高的100家上市公司证券；加权方式：待进一步核验完整权重细则；调样频率：待进一步核验</t>
+        </is>
+      </c>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/1645_931268_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+      <c r="AM56" s="2" t="inlineStr">
+        <is>
+          <t>部分核验：补充观察；前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
         </is>
       </c>
     </row>
@@ -9379,6 +10426,18 @@
       <c r="AG57" s="2" t="inlineStr"/>
       <c r="AH57" s="2" t="inlineStr"/>
       <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK57" s="2" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr"/>
+      <c r="AM57" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -9536,6 +10595,18 @@
       <c r="AG58" s="2" t="inlineStr"/>
       <c r="AH58" s="2" t="inlineStr"/>
       <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr">
+        <is>
+          <t>未匹配</t>
+        </is>
+      </c>
+      <c r="AK58" s="2" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr"/>
+      <c r="AM58" s="2" t="inlineStr">
+        <is>
+          <t>未匹配到指数规则，后续人工核验</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -9709,9 +10780,29 @@
           <t>不混入境内A股主线</t>
         </is>
       </c>
+      <c r="AJ59" s="2" t="inlineStr">
+        <is>
+          <t>部分核验</t>
+        </is>
+      </c>
+      <c r="AK59" s="2" t="inlineStr">
+        <is>
+          <t>港股通低波红利策略，属于跨境补充，不混入境内A股主线；选样方法：标普官网说明该指数用于衡量标普港股通指数内50只波幅最小、收益率高的股票表现；完整规则见标普低波红利指数编制方法；加权方式：待进一步查标普方法论细则；调样频率：待进一步核验</t>
+        </is>
+      </c>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>https://www.spglobal.com/spdji/zh/indices/dividends-factors/sp-access-hong-kong-low-volatility-high-dividend-index/</t>
+        </is>
+      </c>
+      <c r="AM59" s="2" t="inlineStr">
+        <is>
+          <t>部分核验：跨境补充代表；前十大成分股、行业分布待 Wind / 指数官网 factsheet 实时导出</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI59"/>
+  <autoFilter ref="A1:AM59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/01_processed_data/classification/境内策略ETF产品池_代表产品筛选版.xlsx
+++ b/01_processed_data/classification/境内策略ETF产品池_代表产品筛选版.xlsx
@@ -6538,14 +6538,22 @@
       </c>
       <c r="AJ35" s="2" t="inlineStr">
         <is>
-          <t>未匹配</t>
-        </is>
-      </c>
-      <c r="AK35" s="2" t="inlineStr"/>
-      <c r="AL35" s="3" t="inlineStr"/>
+          <t>部分核验</t>
+        </is>
+      </c>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>富国中证价值ETF对应中证国信价值指数，价值策略规则已部分核验，仍需后续补齐加权方式、调样频率和权重限制。</t>
+        </is>
+      </c>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208180210-931052_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
       <c r="AM35" s="2" t="inlineStr">
         <is>
-          <t>未匹配到指数规则，后续人工核验</t>
+          <t>Step8 回写时因跟踪指数名称不一致未匹配，已按基金代码 512040 补写；后续仍需二次核验完整指数规则。</t>
         </is>
       </c>
     </row>
